--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1634F5F9-0767-4D0A-BC4E-03B3255B36B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900D57E9-49E9-4B56-8038-8FBCBC327D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="39">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -153,12 +153,26 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>전원 출석
-- 최윤정지각</t>
+    <t>복습문제</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>복습문제 만점</t>
+    <t>과제 O - 셋팅1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ 기여도 - 복습문제 / 협업마스터</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석
+- 최윤정 지각</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복습문제
+협업마스터 
+- 장영탁, 김현미</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -256,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,18 +289,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -626,6 +634,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -641,7 +809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -765,22 +933,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1074,7 +1287,8 @@
     <col min="4" max="4" width="14.625" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
     <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="8" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1082,25 +1296,25 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="D2" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="51" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="28" t="s">
@@ -1122,36 +1336,36 @@
         <v>4</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="14">
+      <c r="B3" s="56">
         <v>46107</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="10" t="s">
+      <c r="E3" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="45">
+        <v>1</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1160,39 +1374,39 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="15">
+    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="58">
         <v>46108</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="E4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1201,39 +1415,39 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="15">
+      <c r="B5" s="56">
         <v>46111</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="57" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="43" t="s">
+      <c r="E5" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1242,20 +1456,20 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="15">
+      <c r="B6" s="61">
         <v>46112</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="42" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -1264,8 +1478,8 @@
       <c r="F6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="43" t="s">
-        <v>35</v>
+      <c r="G6" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -1274,30 +1488,30 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
+        <v>5</v>
+      </c>
+      <c r="L6" s="35">
+        <v>1</v>
+      </c>
+      <c r="M6" s="35">
+        <v>1</v>
+      </c>
+      <c r="N6" s="31">
         <v>4</v>
       </c>
-      <c r="L6" s="35">
-        <v>1</v>
-      </c>
-      <c r="M6" s="35">
-        <v>1</v>
-      </c>
-      <c r="N6" s="31">
-        <v>2</v>
-      </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="33" x14ac:dyDescent="0.3">
-      <c r="B7" s="15">
+    <row r="7" spans="2:17" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="61">
         <v>46113</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>34</v>
+      <c r="D7" s="42" t="s">
+        <v>37</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>23</v>
@@ -1305,8 +1519,8 @@
       <c r="F7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>23</v>
+      <c r="G7" s="42" t="s">
+        <v>38</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
@@ -1315,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1324,17 +1538,17 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="15">
+      <c r="B8" s="61">
         <v>46114</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1346,9 +1560,7 @@
       <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="G8" s="5"/>
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
@@ -1356,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1365,39 +1577,39 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="15">
+    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="58">
         <v>46115</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1406,39 +1618,39 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="15">
+      <c r="B10" s="56">
         <v>46118</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="D10" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1447,17 +1659,17 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="15">
+      <c r="B11" s="61">
         <v>46119</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="53" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1479,7 +1691,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1488,17 +1700,17 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="15">
+      <c r="B12" s="61">
         <v>46120</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="53" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1520,26 +1732,26 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
+        <v>5</v>
+      </c>
+      <c r="L12" s="35">
+        <v>1</v>
+      </c>
+      <c r="M12" s="35">
+        <v>1</v>
+      </c>
+      <c r="N12" s="31">
         <v>4</v>
       </c>
-      <c r="L12" s="35">
-        <v>1</v>
-      </c>
-      <c r="M12" s="35">
-        <v>1</v>
-      </c>
-      <c r="N12" s="31">
-        <v>2</v>
-      </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="15">
+      <c r="B13" s="61">
         <v>46121</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1561,7 +1773,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -1570,39 +1782,39 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="15">
+    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="58">
         <v>46122</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="6" t="s">
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -1611,39 +1823,39 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="15">
+      <c r="B15" s="56">
         <v>46125</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="D15" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="46" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -1652,17 +1864,17 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="15">
+      <c r="B16" s="61">
         <v>46126</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="53" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1683,8 +1895,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="30">
-        <v>4</v>
+      <c r="K16" s="43">
+        <v>5</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -1692,18 +1904,18 @@
       <c r="M16" s="39">
         <v>1</v>
       </c>
-      <c r="N16" s="31">
-        <v>2</v>
+      <c r="N16" s="41">
+        <v>3</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="15">
+      <c r="B17" s="61">
         <v>46127</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="53" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -1723,10 +1935,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="15">
+      <c r="B18" s="61">
         <v>46128</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1745,57 +1957,57 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="15">
+    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="58">
         <v>46129</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="15">
+      <c r="B20" s="56">
         <v>46132</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="D20" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="46" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="15">
+      <c r="B21" s="61">
         <v>46133</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="53" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -1815,10 +2027,10 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="15">
+      <c r="B22" s="61">
         <v>46134</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="53" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1838,10 +2050,10 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="15">
+      <c r="B23" s="61">
         <v>46135</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -1860,57 +2072,57 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="15">
+    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="58">
         <v>46136</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="6" t="s">
+      <c r="D24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="15">
+      <c r="B25" s="54">
         <v>46139</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="D25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="15">
+      <c r="B26" s="52">
         <v>46140</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="53" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -1925,15 +2137,15 @@
       <c r="G26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="15">
+      <c r="B27" s="52">
         <v>46141</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="53" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -1948,30 +2160,30 @@
       <c r="G27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="16">
+      <c r="H27" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="52">
         <v>46142</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="53" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="8" t="s">
+      <c r="E28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>23</v>
       </c>
     </row>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900D57E9-49E9-4B56-8038-8FBCBC327D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8190BB-AC02-4BE3-AD2E-58ADF7E5D978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="42">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -170,9 +170,37 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>복습문제
+    <r>
+      <t xml:space="preserve">복습문제
 협업마스터 
-- 장영탁, 김현미</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이일두님추천
+- 장영탁, 김현미
+최다영추천 - 정수정</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>7일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>12일</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK-CONTROL</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +211,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +297,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -294,7 +331,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -794,6 +831,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -809,7 +855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -994,6 +1040,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1284,7 +1333,7 @@
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
     <col min="6" max="6" width="14.25" customWidth="1"/>
     <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
@@ -1365,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1374,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1406,7 +1455,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1415,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1447,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1456,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1488,22 +1537,22 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
+        <v>6</v>
+      </c>
+      <c r="L6" s="35">
+        <v>1</v>
+      </c>
+      <c r="M6" s="35">
+        <v>1</v>
+      </c>
+      <c r="N6" s="31">
         <v>5</v>
       </c>
-      <c r="L6" s="35">
-        <v>1</v>
-      </c>
-      <c r="M6" s="35">
-        <v>1</v>
-      </c>
-      <c r="N6" s="31">
-        <v>4</v>
-      </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="69.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="61">
         <v>46113</v>
       </c>
@@ -1529,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1538,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1551,8 +1600,8 @@
       <c r="C8" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
+      <c r="D8" s="44" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>23</v>
@@ -1560,7 +1609,9 @@
       <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="42" t="s">
+        <v>34</v>
+      </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
@@ -1568,22 +1619,22 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
+        <v>5</v>
+      </c>
+      <c r="L8" s="35">
+        <v>1</v>
+      </c>
+      <c r="M8" s="35">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31">
         <v>4</v>
       </c>
-      <c r="L8" s="35">
-        <v>1</v>
-      </c>
-      <c r="M8" s="35">
-        <v>1</v>
-      </c>
-      <c r="N8" s="31">
-        <v>3</v>
-      </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="58">
         <v>46115</v>
       </c>
@@ -1594,22 +1645,25 @@
         <v>23</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>39</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1618,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1650,7 +1704,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -1659,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -1691,7 +1745,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -1700,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -1732,16 +1786,16 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
+        <v>6</v>
+      </c>
+      <c r="L12" s="35">
+        <v>1</v>
+      </c>
+      <c r="M12" s="35">
+        <v>1</v>
+      </c>
+      <c r="N12" s="31">
         <v>5</v>
-      </c>
-      <c r="L12" s="35">
-        <v>1</v>
-      </c>
-      <c r="M12" s="35">
-        <v>1</v>
-      </c>
-      <c r="N12" s="31">
-        <v>4</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -1773,16 +1827,16 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
+        <v>6</v>
+      </c>
+      <c r="L13" s="35">
+        <v>1</v>
+      </c>
+      <c r="M13" s="35">
+        <v>1</v>
+      </c>
+      <c r="N13" s="31">
         <v>5</v>
-      </c>
-      <c r="L13" s="35">
-        <v>1</v>
-      </c>
-      <c r="M13" s="35">
-        <v>1</v>
-      </c>
-      <c r="N13" s="31">
-        <v>3</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -1810,11 +1864,14 @@
       <c r="H14" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="I14" s="62" t="s">
+        <v>40</v>
+      </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -1823,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -1855,7 +1912,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -1864,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -1896,7 +1953,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -1905,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sally03915\Desktop\2026.03-ing\2026-출석부\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EA39DD-59D0-47DC-83C5-9253E70B6C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="2026.9" sheetId="6" r:id="rId6"/>
     <sheet name="2026.10" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -233,19 +232,34 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 복습문제
+    <r>
+      <t xml:space="preserve"> 복습문제
 html - css-ckeck1
 java - 계산기1
 java - 성적처리
 협업마스터
 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>김욱진님추천 
+- 김보라-하혜원</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
@@ -1360,24 +1374,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.69921875" customWidth="1"/>
+    <col min="6" max="6" width="14.19921875" customWidth="1"/>
+    <col min="7" max="7" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:17" ht="49.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="46" t="s">
         <v>30</v>
       </c>
@@ -1421,7 +1435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B3" s="55">
         <v>46107</v>
       </c>
@@ -1456,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="57">
         <v>46108</v>
       </c>
@@ -1503,7 +1517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="55">
         <v>46111</v>
       </c>
@@ -1544,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B6" s="60">
         <v>46112</v>
       </c>
@@ -1585,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="69.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="60">
         <v>46266</v>
       </c>
@@ -1626,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="45" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" ht="46.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="60">
         <v>46267</v>
       </c>
@@ -1667,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="99.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="109.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="57">
         <v>46268</v>
       </c>
@@ -1711,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="55">
         <v>46271</v>
       </c>
@@ -1752,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="60">
         <v>46272</v>
       </c>
@@ -1793,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="60">
         <v>46273</v>
       </c>
@@ -1834,7 +1848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="60">
         <v>46274</v>
       </c>
@@ -1875,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B14" s="57">
         <v>46275</v>
       </c>
@@ -1919,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="55">
         <v>46278</v>
       </c>
@@ -1960,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="60">
         <v>46284</v>
       </c>
@@ -1995,13 +2009,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="60">
         <v>46127</v>
       </c>
@@ -2024,7 +2038,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="60">
         <v>46128</v>
       </c>
@@ -2047,7 +2061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="57">
         <v>46129</v>
       </c>
@@ -2070,7 +2084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="55">
         <v>46132</v>
       </c>
@@ -2093,7 +2107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="60">
         <v>46133</v>
       </c>
@@ -2116,7 +2130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="60">
         <v>46134</v>
       </c>
@@ -2139,7 +2153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="60">
         <v>46135</v>
       </c>
@@ -2162,7 +2176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2185,7 +2199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2208,7 +2222,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2231,7 +2245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="51">
         <v>46141</v>
       </c>
@@ -2254,7 +2268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2277,7 +2291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2299,19 +2313,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -2355,7 +2369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -2386,7 +2400,7 @@
       <c r="N3" s="31"/>
       <c r="O3" s="32"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -2417,7 +2431,7 @@
       <c r="N4" s="35"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -2448,7 +2462,7 @@
       <c r="N5" s="35"/>
       <c r="O5" s="36"/>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -2479,7 +2493,7 @@
       <c r="N6" s="35"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -2510,7 +2524,7 @@
       <c r="N7" s="35"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -2541,7 +2555,7 @@
       <c r="N8" s="35"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -2572,7 +2586,7 @@
       <c r="N9" s="35"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -2603,7 +2617,7 @@
       <c r="N10" s="35"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -2634,7 +2648,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -2665,7 +2679,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -2696,7 +2710,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="36"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -2727,7 +2741,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="36"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -2758,7 +2772,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="36"/>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -2789,7 +2803,7 @@
       <c r="N16" s="39"/>
       <c r="O16" s="40"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -2812,7 +2826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -2835,7 +2849,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -2858,7 +2872,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -2881,7 +2895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -2904,7 +2918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -2927,7 +2941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -2950,7 +2964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -2973,7 +2987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -2996,7 +3010,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -3019,7 +3033,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -3042,7 +3056,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -3065,7 +3079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -3074,10 +3088,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -3087,15 +3101,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3139,7 +3153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -3180,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -3221,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -3262,7 +3276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -3303,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -3344,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -3385,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -3426,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -3467,7 +3481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -3508,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -3549,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -3590,7 +3604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -3631,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -3672,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -3713,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -3736,7 +3750,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -3759,7 +3773,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -3782,7 +3796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -3805,7 +3819,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -3828,7 +3842,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -3851,7 +3865,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -3874,7 +3888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -3897,7 +3911,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -3920,7 +3934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -3943,7 +3957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -3966,7 +3980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -3989,7 +4003,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -3998,10 +4012,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4011,15 +4025,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -4063,7 +4077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -4104,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -4145,7 +4159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -4186,7 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -4227,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -4268,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -4309,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -4350,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -4391,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -4432,7 +4446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -4473,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -4514,7 +4528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -4555,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -4596,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -4637,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -4660,7 +4674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -4683,7 +4697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -4706,7 +4720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -4729,7 +4743,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -4752,7 +4766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -4775,7 +4789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -4798,7 +4812,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -4821,7 +4835,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -4844,7 +4858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -4867,7 +4881,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -4890,7 +4904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -4913,7 +4927,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -4922,10 +4936,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -4935,15 +4949,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -4987,7 +5001,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5028,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -5069,7 +5083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -5110,7 +5124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -5151,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -5192,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -5233,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -5274,7 +5288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -5315,7 +5329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -5356,7 +5370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -5397,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -5438,7 +5452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -5479,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -5520,7 +5534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -5561,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -5584,7 +5598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -5607,7 +5621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -5630,7 +5644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -5653,7 +5667,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -5676,7 +5690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -5699,7 +5713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -5722,7 +5736,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -5745,7 +5759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -5768,7 +5782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -5791,7 +5805,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -5814,7 +5828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -5837,7 +5851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -5846,10 +5860,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -5859,15 +5873,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -5911,7 +5925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -5952,7 +5966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -5993,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6034,7 +6048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -6075,7 +6089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -6116,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -6157,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -6198,7 +6212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -6239,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -6280,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -6321,7 +6335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -6362,7 +6376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -6403,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -6444,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -6485,7 +6499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -6508,7 +6522,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -6531,7 +6545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -6554,7 +6568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -6577,7 +6591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -6600,7 +6614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -6623,7 +6637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -6646,7 +6660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -6669,7 +6683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -6692,7 +6706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -6715,7 +6729,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -6738,7 +6752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -6761,7 +6775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -6770,10 +6784,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>
@@ -6783,15 +6797,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="2:17" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" ht="87.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -6835,7 +6849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="14">
         <v>46107</v>
       </c>
@@ -6876,7 +6890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="15">
         <v>46108</v>
       </c>
@@ -6917,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B5" s="15">
         <v>46111</v>
       </c>
@@ -6958,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="15">
         <v>46112</v>
       </c>
@@ -6999,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="15">
         <v>46113</v>
       </c>
@@ -7040,7 +7054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="15">
         <v>46114</v>
       </c>
@@ -7081,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="15">
         <v>46115</v>
       </c>
@@ -7122,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="15">
         <v>46118</v>
       </c>
@@ -7163,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11" s="15">
         <v>46119</v>
       </c>
@@ -7204,7 +7218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="15">
         <v>46120</v>
       </c>
@@ -7245,7 +7259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="15">
         <v>46121</v>
       </c>
@@ -7286,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="15">
         <v>46122</v>
       </c>
@@ -7327,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="15">
         <v>46125</v>
       </c>
@@ -7368,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15">
         <v>46126</v>
       </c>
@@ -7409,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="15">
         <v>46127</v>
       </c>
@@ -7432,7 +7446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="15">
         <v>46128</v>
       </c>
@@ -7455,7 +7469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="15">
         <v>46129</v>
       </c>
@@ -7478,7 +7492,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B20" s="15">
         <v>46132</v>
       </c>
@@ -7501,7 +7515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B21" s="15">
         <v>46133</v>
       </c>
@@ -7524,7 +7538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B22" s="15">
         <v>46134</v>
       </c>
@@ -7547,7 +7561,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="15">
         <v>46135</v>
       </c>
@@ -7570,7 +7584,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B24" s="15">
         <v>46136</v>
       </c>
@@ -7593,7 +7607,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B25" s="15">
         <v>46139</v>
       </c>
@@ -7616,7 +7630,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B26" s="15">
         <v>46140</v>
       </c>
@@ -7639,7 +7653,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B27" s="15">
         <v>46141</v>
       </c>
@@ -7662,7 +7676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B28" s="16">
         <v>46142</v>
       </c>
@@ -7685,7 +7699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2"/>
@@ -7694,10 +7708,10 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C31" s="3"/>
     </row>
   </sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3006F647-0730-4E14-8FA2-B6D2EB68B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE5C051-85CF-4ACF-9B53-7DF520A315DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="735" windowWidth="13650" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="54">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -171,10 +171,6 @@
   </si>
   <si>
     <t>7일</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>12일</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -330,6 +326,9 @@
       <t>욱진, 윤정, 보라, 주협</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>13일</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1601,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1642,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1706,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
@@ -1724,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1747,7 +1746,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
@@ -1765,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1779,16 +1778,16 @@
         <v>26</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="7">
         <v>1</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>23</v>
@@ -1809,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1823,7 +1822,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>23</v>
@@ -1832,7 +1831,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" s="45" t="s">
         <v>23</v>
@@ -1850,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -1864,7 +1863,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>23</v>
@@ -1873,7 +1872,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1891,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -1905,7 +1904,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
@@ -1914,7 +1913,7 @@
         <v>23</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>23</v>
@@ -1932,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -1940,19 +1939,22 @@
     </row>
     <row r="13" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
+      <c r="D13" s="43" t="s">
+        <v>48</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>23</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
@@ -1970,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -1999,7 +2001,7 @@
         <v>23</v>
       </c>
       <c r="I14" s="61" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
@@ -2014,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2055,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2096,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2334,7 +2336,7 @@
     </row>
     <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>29</v>
@@ -2388,7 +2390,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H29" s="2"/>
     </row>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB280CFA-7823-4FB5-B1BC-62401A2D713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200C9D8B-CC9E-42E1-B640-A376D7E58129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="64">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -396,6 +396,16 @@
 장영탁(마스터)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> 복습문제
+협업마스터-</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석 
+- 이일두님 조퇴예정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -541,7 +551,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1040,17 +1050,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1117,7 +1116,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1304,31 +1303,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1700,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1709,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1741,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1750,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1782,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1791,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1823,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1832,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1867,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1876,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1911,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1920,32 +1916,32 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="111" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="64">
+      <c r="B9" s="63">
         <v>46115</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="E9" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="67">
-        <v>1</v>
-      </c>
-      <c r="G9" s="68" t="s">
+      <c r="F9" s="66">
+        <v>1</v>
+      </c>
+      <c r="G9" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="68" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="61" t="s">
@@ -1955,7 +1951,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1964,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -1992,14 +1988,14 @@
       <c r="H10" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="62" t="s">
         <v>55</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2008,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2040,7 +2036,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2049,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2077,14 +2073,14 @@
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="62" t="s">
         <v>56</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2093,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2121,14 +2117,14 @@
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="62" t="s">
         <v>57</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2137,42 +2133,42 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="64">
+      <c r="B14" s="63">
         <v>46123</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="68" t="s">
+      <c r="D14" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="68" t="s">
+      <c r="E14" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="63" t="s">
+      <c r="H14" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="62" t="s">
         <v>59</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2181,13 +2177,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="66" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="55">
         <v>46125</v>
       </c>
@@ -2209,14 +2205,14 @@
       <c r="H15" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="63" t="s">
+      <c r="I15" s="62" t="s">
         <v>61</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2225,21 +2221,21 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="60">
         <v>46126</v>
       </c>
       <c r="C16" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>23</v>
+      <c r="D16" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>23</v>
@@ -2247,8 +2243,8 @@
       <c r="F16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>23</v>
+      <c r="G16" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>23</v>
@@ -2256,8 +2252,8 @@
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="62">
-        <v>13</v>
+      <c r="K16" s="30">
+        <v>14</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2266,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2342,7 +2338,7 @@
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="70">
+      <c r="B20" s="69">
         <v>46132</v>
       </c>
       <c r="C20" s="54" t="s">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200C9D8B-CC9E-42E1-B640-A376D7E58129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC38C5F-94C8-43D6-81D9-8CF8287BA302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="65">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -406,6 +406,11 @@
 - 이일두님 조퇴예정</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">  복습문제 손에 모터단 친구들( 수정, 윤정, 대원)
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1116,7 +1121,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1325,6 +1330,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2249,11 +2257,14 @@
       <c r="H16" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="I16" s="70" t="s">
+        <v>64</v>
+      </c>
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2262,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2570,7 +2581,7 @@
   <dimension ref="B1:Q31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD1B683-9AD8-4595-AFF0-A927A9A44287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59647A7F-2910-44D6-B938-7E5DDFEA231F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34650" yWindow="435" windowWidth="22905" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="68">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -418,6 +418,12 @@
   </si>
   <si>
     <t xml:space="preserve"> 복습문제 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">복습문제 체크 - 다영 (3)
+복습문제 신의손 - 윤정 (3),  보라,  수정, 욱진, 대원
+협업마스터 - 주엽, 일두 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1736,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1777,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1818,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1859,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1903,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1947,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1991,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2035,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2076,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2120,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2164,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2208,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2252,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2296,13 +2302,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B17" s="60">
         <v>46127</v>
       </c>
@@ -2324,8 +2330,11 @@
       <c r="H17" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="60">
         <v>46128</v>
       </c>
@@ -2348,7 +2357,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="57">
         <v>46129</v>
       </c>
@@ -2371,7 +2380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="69">
         <v>46132</v>
       </c>
@@ -2394,7 +2403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="60">
         <v>46133</v>
       </c>
@@ -2417,7 +2426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="60">
         <v>46134</v>
       </c>
@@ -2440,7 +2449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="60">
         <v>46135</v>
       </c>
@@ -2463,7 +2472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
@@ -2486,7 +2495,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
@@ -2509,7 +2518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2532,7 +2541,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
         <v>49</v>
       </c>
@@ -2555,7 +2564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2578,7 +2587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59647A7F-2910-44D6-B938-7E5DDFEA231F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA95117-FEA8-4E52-AB61-6AFB5EC98E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34650" yWindow="435" windowWidth="22905" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29595" yWindow="15" windowWidth="8370" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="68">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -167,10 +167,6 @@
   <si>
     <t>전원 출석
 - 최윤정 지각</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BANK-CONTROL</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -417,13 +413,19 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 복습문제 </t>
+    <t xml:space="preserve">복습문제 체크 - 다영 (3)
+복습문제 신의손 - 윤정 (3),  보라,  수정, 욱진, 대원
+협업마스터 - 주엽, 일두 </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">복습문제 체크 - 다영 (3)
-복습문제 신의손 - 윤정 (3),  보라,  수정, 욱진, 대원
-협업마스터 - 주엽, 일두 </t>
+    <t xml:space="preserve"> 復習문제 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 복습문제 
+협업마스터 
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1733,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1742,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1774,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1783,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1815,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1824,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1856,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1865,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1888,19 +1890,19 @@
         <v>23</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1909,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1932,19 +1934,19 @@
         <v>23</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1953,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1967,28 +1969,28 @@
         <v>26</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="66">
-        <v>1</v>
+      <c r="E9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G9" s="67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="68" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1997,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2011,7 +2013,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>23</v>
@@ -2020,19 +2022,19 @@
         <v>23</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" s="45" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="33" t="s">
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2041,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2055,7 +2057,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>23</v>
@@ -2064,7 +2066,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -2073,7 +2075,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2082,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2096,7 +2098,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
@@ -2105,19 +2107,19 @@
         <v>23</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2126,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2134,13 +2136,13 @@
     </row>
     <row r="13" spans="2:17" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B13" s="60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>23</v>
@@ -2149,19 +2151,19 @@
         <v>23</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2170,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2184,7 +2186,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="66" t="s">
         <v>23</v>
@@ -2193,19 +2195,19 @@
         <v>23</v>
       </c>
       <c r="G14" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="62" t="s">
         <v>58</v>
-      </c>
-      <c r="H14" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="62" t="s">
-        <v>59</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2214,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2228,7 +2230,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" s="44" t="s">
         <v>23</v>
@@ -2237,19 +2239,19 @@
         <v>23</v>
       </c>
       <c r="G15" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="62" t="s">
         <v>60</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="62" t="s">
-        <v>61</v>
       </c>
       <c r="J15" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2258,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2272,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>23</v>
@@ -2281,19 +2283,19 @@
         <v>23</v>
       </c>
       <c r="G16" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="70" t="s">
         <v>62</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="70" t="s">
-        <v>63</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="71">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2302,13 +2304,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="60">
         <v>46127</v>
       </c>
@@ -2316,7 +2318,7 @@
         <v>29</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>23</v>
@@ -2331,18 +2333,18 @@
         <v>23</v>
       </c>
       <c r="I17" s="70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B18" s="60">
         <v>46128</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>23</v>
+      <c r="D18" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
@@ -2350,8 +2352,8 @@
       <c r="F18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>23</v>
+      <c r="G18" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>23</v>
@@ -2543,7 +2545,7 @@
     </row>
     <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>29</v>
@@ -2597,7 +2599,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H29" s="2"/>
     </row>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA95117-FEA8-4E52-AB61-6AFB5EC98E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7DF5B2-B8A9-429E-99CB-3855F522C4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29595" yWindow="15" windowWidth="8370" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="69">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -426,6 +426,11 @@
     <t xml:space="preserve"> 복습문제 
 협업마스터 
 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>협업마스터 - 김주엽, 최윤정, 손예진, 김욱진, 
+김보라, 이일두</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1735,7 +1740,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1744,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1776,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1785,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1817,7 +1822,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1826,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1858,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1867,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1902,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1911,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1946,7 +1951,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1955,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -1990,7 +1995,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -1999,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2034,7 +2039,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2043,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2075,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2084,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2119,7 +2124,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2128,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2163,7 +2168,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2172,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2207,7 +2212,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2216,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2251,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2260,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2304,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
@@ -2357,6 +2362,9 @@
       </c>
       <c r="H18" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I18" s="62" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55B0CBE-62C1-4109-8CCB-9FEC8F2C0D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBBDB0F-82FC-4498-ADF0-72C791FC4180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="73">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -452,6 +474,15 @@
   </si>
   <si>
     <t>수정, 채연, 다영, 예진</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 복습문제  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원 출석
+-  장영탁 결석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1669,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:Q29"/>
+  <dimension ref="B1:Q30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
@@ -1755,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -1764,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
@@ -1796,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -1805,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -1837,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -1846,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -1878,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -1887,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -1922,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -1931,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -1966,7 +1997,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -1975,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -2010,7 +2041,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -2019,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
@@ -2054,7 +2085,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -2063,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -2095,7 +2126,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -2104,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
@@ -2139,7 +2170,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -2148,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
@@ -2183,7 +2214,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -2192,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
@@ -2227,7 +2258,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -2236,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
@@ -2271,7 +2302,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L15" s="35">
         <v>1</v>
@@ -2280,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -2315,7 +2346,7 @@
         <v>18</v>
       </c>
       <c r="K16" s="70">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -2324,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="59">
         <v>46127</v>
       </c>
@@ -2355,8 +2386,12 @@
       <c r="I17" s="69" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P17" cm="1">
+        <f t="array" ref="P17:P30">N3:N16+1</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="59">
         <v>46128</v>
       </c>
@@ -2381,8 +2416,11 @@
       <c r="I18" s="61" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P18">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="57">
         <v>46129</v>
       </c>
@@ -2404,8 +2442,11 @@
       <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P19">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="68">
         <v>46132</v>
       </c>
@@ -2427,8 +2468,11 @@
       <c r="H20" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P20">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="59">
         <v>46133</v>
       </c>
@@ -2453,8 +2497,11 @@
       <c r="I21" s="61" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="59">
         <v>46134</v>
       </c>
@@ -2470,22 +2517,25 @@
       <c r="F22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>23</v>
+      <c r="G22" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="59">
         <v>46135</v>
       </c>
       <c r="C23" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>23</v>
+      <c r="D23" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>23</v>
@@ -2493,22 +2543,25 @@
       <c r="F23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>23</v>
+      <c r="G23" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="57">
         <v>46136</v>
       </c>
       <c r="C24" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>23</v>
+      <c r="D24" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>23</v>
@@ -2516,22 +2569,25 @@
       <c r="F24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="G24" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P24">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="33" x14ac:dyDescent="0.3">
       <c r="B25" s="53">
         <v>46139</v>
       </c>
       <c r="C25" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>23</v>
+      <c r="D25" s="42" t="s">
+        <v>72</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>23</v>
@@ -2545,8 +2601,11 @@
       <c r="H25" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="51">
         <v>46140</v>
       </c>
@@ -2568,8 +2627,11 @@
       <c r="H26" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="P26">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="51" t="s">
         <v>48</v>
       </c>
@@ -2591,8 +2653,11 @@
       <c r="H27" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P27">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="51">
         <v>46142</v>
       </c>
@@ -2614,8 +2679,11 @@
       <c r="H28" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="P28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="4"/>
       <c r="D29" s="2">
@@ -2628,6 +2696,14 @@
         <v>39</v>
       </c>
       <c r="H29" s="2"/>
+      <c r="P29">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="P30">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D87E8A-D027-402D-BD09-6384986F98F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C66B1A7-79AA-4234-827D-811E2166EF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026. 3~4월" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="81">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -500,6 +500,11 @@
 윤정6</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>전원 출석
+- 하혜원외출</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -654,7 +659,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1205,17 +1210,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1518,29 +1512,26 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1551,16 +1542,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1570,6 +1555,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2899,7 +2893,7 @@
       <c r="C3" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -2921,7 +2915,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="31">
         <v>1</v>
@@ -2930,21 +2924,21 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="75" t="s">
-        <v>21</v>
+      <c r="D4" s="86" t="s">
+        <v>80</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>23</v>
@@ -2953,7 +2947,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>23</v>
@@ -2962,7 +2956,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" s="35">
         <v>1</v>
@@ -2971,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="31">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="36">
         <v>0</v>
@@ -2984,7 +2978,7 @@
       <c r="C5" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="D5" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="65" t="s">
@@ -3003,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" s="35">
         <v>1</v>
@@ -3012,39 +3006,39 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="79">
+      <c r="B6" s="78">
         <v>46153</v>
       </c>
       <c r="C6" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="81" t="s">
+      <c r="E6" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="80" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="33" t="s">
         <v>8</v>
       </c>
       <c r="K6" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" s="35">
         <v>1</v>
@@ -3053,20 +3047,20 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="79">
+      <c r="B7" s="78">
         <v>46154</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -3085,7 +3079,7 @@
         <v>9</v>
       </c>
       <c r="K7" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" s="35">
         <v>1</v>
@@ -3094,20 +3088,20 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="79">
+      <c r="B8" s="78">
         <v>46155</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -3126,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" s="35">
         <v>1</v>
@@ -3135,20 +3129,20 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="79">
+      <c r="B9" s="78">
         <v>46156</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -3167,7 +3161,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" s="35">
         <v>1</v>
@@ -3176,20 +3170,20 @@
         <v>1</v>
       </c>
       <c r="N9" s="31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O9" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="79">
+      <c r="B10" s="78">
         <v>46157</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -3208,7 +3202,7 @@
         <v>12</v>
       </c>
       <c r="K10" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" s="35">
         <v>1</v>
@@ -3217,20 +3211,20 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="79">
+      <c r="B11" s="78">
         <v>46160</v>
       </c>
       <c r="C11" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="44" t="s">
@@ -3249,7 +3243,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" s="35">
         <v>1</v>
@@ -3258,20 +3252,20 @@
         <v>1</v>
       </c>
       <c r="N11" s="31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="79">
+      <c r="B12" s="78">
         <v>46161</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -3290,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="K12" s="30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L12" s="35">
         <v>1</v>
@@ -3299,20 +3293,20 @@
         <v>1</v>
       </c>
       <c r="N12" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="79">
+      <c r="B13" s="78">
         <v>46162</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -3331,7 +3325,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L13" s="35">
         <v>1</v>
@@ -3340,20 +3334,20 @@
         <v>1</v>
       </c>
       <c r="N13" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="79">
+      <c r="B14" s="78">
         <v>46163</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="87" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -3372,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="K14" s="30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L14" s="35">
         <v>1</v>
@@ -3381,20 +3375,20 @@
         <v>1</v>
       </c>
       <c r="N14" s="31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O14" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="79">
+      <c r="B15" s="78">
         <v>46164</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="7" t="s">
@@ -3413,48 +3407,48 @@
         <v>17</v>
       </c>
       <c r="K15" s="30">
+        <v>28</v>
+      </c>
+      <c r="L15" s="35">
+        <v>1</v>
+      </c>
+      <c r="M15" s="35">
+        <v>1</v>
+      </c>
+      <c r="N15" s="31">
+        <v>42</v>
+      </c>
+      <c r="O15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="81">
+        <v>46167</v>
+      </c>
+      <c r="C16" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="35">
-        <v>1</v>
-      </c>
-      <c r="M15" s="35">
-        <v>1</v>
-      </c>
-      <c r="N15" s="31">
-        <v>41</v>
-      </c>
-      <c r="O15" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="84">
-        <v>46167</v>
-      </c>
-      <c r="C16" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="88" t="s">
+      <c r="E16" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="85" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>77</v>
       </c>
       <c r="K16" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="39">
         <v>1</v>
@@ -3463,20 +3457,20 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="79">
+      <c r="B17" s="78">
         <v>46168</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -3493,13 +3487,13 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="79">
+      <c r="B18" s="78">
         <v>46169</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="87" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -3516,13 +3510,13 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="79">
+      <c r="B19" s="78">
         <v>46170</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -3539,13 +3533,13 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="79">
+      <c r="B20" s="78">
         <v>46171</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="86" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="5" t="s">

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C66B1A7-79AA-4234-827D-811E2166EF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0678BEE-4CC9-41ED-8B8F-0BB59E47B180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="82">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -505,6 +505,13 @@
 - 하혜원외출</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>협업마스터 - 일두
+예진 , 윤정 , 혜원 , 현미 , 보라
+금일 신의손~주엽, 
+대원,   보라, 예진,윤정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -659,7 +666,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1283,6 +1290,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1298,7 +1316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1564,6 +1582,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2835,7 +2859,7 @@
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
+    <col min="9" max="9" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2924,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="31">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O3" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" ht="99.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
@@ -2951,6 +2975,9 @@
       </c>
       <c r="H4" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="I4" s="89" t="s">
+        <v>81</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>6</v>
@@ -3006,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="36">
         <v>0</v>
@@ -3047,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" s="36">
         <v>0</v>
@@ -3088,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" s="36">
         <v>0</v>
@@ -3129,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="31">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O8" s="36">
         <v>0</v>
@@ -3211,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O10" s="36">
         <v>0</v>
@@ -3416,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="31">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O15" s="36">
         <v>0</v>
@@ -3447,7 +3474,7 @@
       <c r="J16" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="90">
         <v>27</v>
       </c>
       <c r="L16" s="39">
@@ -3457,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="41">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O16" s="40">
         <v>0</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713C20F5-3F7A-47EC-B8DF-59007A3C0066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C4A75D-26BF-40EC-9566-38D56BB7905A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="119">
   <si>
     <t>출석일수 (Attendance Days)</t>
   </si>
@@ -1036,6 +1036,11 @@
     <t>윤정, 주엽, 채연, 보라</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>전원 출석
+-손창기외</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1946,7 +1951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2254,9 +2259,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3679,7 +3681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
@@ -3688,11 +3690,11 @@
     <col min="10" max="10" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17.25" thickBot="1">
+    <row r="1" spans="1:19" ht="17.25" thickBot="1">
       <c r="B1" s="1"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:18" ht="83.25" thickBot="1">
+    <row r="2" spans="1:19" ht="83.25" thickBot="1">
       <c r="B2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3736,7 +3738,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17.25" thickBot="1">
+    <row r="3" spans="1:19" ht="17.25" thickBot="1">
       <c r="B3" s="73">
         <v>46148</v>
       </c>
@@ -3766,7 +3768,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M3" s="35">
         <v>1</v>
@@ -3774,14 +3776,17 @@
       <c r="N3" s="35">
         <v>1</v>
       </c>
-      <c r="O3" s="102">
-        <v>39</v>
+      <c r="O3" s="95">
+        <v>45</v>
       </c>
       <c r="P3" s="36">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="99.75" thickBot="1">
+      <c r="S3" s="95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="99.75" thickBot="1">
       <c r="B4" s="14">
         <v>46149</v>
       </c>
@@ -3811,7 +3816,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M4" s="35">
         <v>1</v>
@@ -3819,14 +3824,14 @@
       <c r="N4" s="35">
         <v>1</v>
       </c>
-      <c r="O4" s="102">
-        <v>39</v>
+      <c r="O4" s="95">
+        <v>45</v>
       </c>
       <c r="P4" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="50.25" thickBot="1">
+    <row r="5" spans="1:19" ht="50.25" thickBot="1">
       <c r="B5" s="76">
         <v>46150</v>
       </c>
@@ -3855,7 +3860,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M5" s="35">
         <v>1</v>
@@ -3863,14 +3868,14 @@
       <c r="N5" s="35">
         <v>1</v>
       </c>
-      <c r="O5" s="102">
-        <v>37</v>
+      <c r="O5" s="95">
+        <v>43</v>
       </c>
       <c r="P5" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="33.75" thickBot="1">
+    <row r="6" spans="1:19" ht="33.75" thickBot="1">
       <c r="B6" s="78">
         <v>46153</v>
       </c>
@@ -3899,7 +3904,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M6" s="35">
         <v>1</v>
@@ -3907,14 +3912,14 @@
       <c r="N6" s="35">
         <v>1</v>
       </c>
-      <c r="O6" s="102">
-        <v>35</v>
+      <c r="O6" s="95">
+        <v>41</v>
       </c>
       <c r="P6" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="33.75" thickBot="1">
+    <row r="7" spans="1:19" ht="33.75" thickBot="1">
       <c r="A7" s="1">
         <v>31</v>
       </c>
@@ -3925,7 +3930,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>23</v>
@@ -3946,7 +3951,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M7" s="35">
         <v>1</v>
@@ -3954,14 +3959,14 @@
       <c r="N7" s="35">
         <v>1</v>
       </c>
-      <c r="O7" s="102">
-        <v>34</v>
+      <c r="O7" s="95">
+        <v>40</v>
       </c>
       <c r="P7" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.25" thickBot="1">
+    <row r="8" spans="1:19" ht="33.75" thickBot="1">
       <c r="B8" s="78">
         <v>46155</v>
       </c>
@@ -3969,7 +3974,7 @@
         <v>29</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>23</v>
@@ -3987,7 +3992,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M8" s="35">
         <v>1</v>
@@ -3995,14 +4000,14 @@
       <c r="N8" s="35">
         <v>1</v>
       </c>
-      <c r="O8" s="102">
-        <v>39</v>
+      <c r="O8" s="95">
+        <v>45</v>
       </c>
       <c r="P8" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.25" thickBot="1">
+    <row r="9" spans="1:19" ht="33.75" thickBot="1">
       <c r="B9" s="78">
         <v>46156</v>
       </c>
@@ -4010,7 +4015,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
@@ -4028,7 +4033,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="35">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M9" s="35">
         <v>1</v>
@@ -4036,14 +4041,14 @@
       <c r="N9" s="35">
         <v>1</v>
       </c>
-      <c r="O9" s="102">
-        <v>33</v>
+      <c r="O9" s="95">
+        <v>39</v>
       </c>
       <c r="P9" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.25" thickBot="1">
+    <row r="10" spans="1:19" ht="33.75" thickBot="1">
       <c r="B10" s="78">
         <v>46157</v>
       </c>
@@ -4051,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>23</v>
@@ -4069,7 +4074,7 @@
         <v>12</v>
       </c>
       <c r="L10" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M10" s="35">
         <v>1</v>
@@ -4077,14 +4082,17 @@
       <c r="N10" s="35">
         <v>1</v>
       </c>
-      <c r="O10" s="102">
-        <v>33</v>
+      <c r="O10" s="95">
+        <v>39</v>
       </c>
       <c r="P10" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17.25" thickBot="1">
+    <row r="11" spans="1:19" ht="33.75" thickBot="1">
+      <c r="A11">
+        <v>35</v>
+      </c>
       <c r="B11" s="78">
         <v>46160</v>
       </c>
@@ -4092,7 +4100,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="E11" s="44" t="s">
         <v>23</v>
@@ -4110,7 +4118,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M11" s="35">
         <v>1</v>
@@ -4118,14 +4126,14 @@
       <c r="N11" s="35">
         <v>1</v>
       </c>
-      <c r="O11" s="102">
-        <v>36</v>
+      <c r="O11" s="95">
+        <v>42</v>
       </c>
       <c r="P11" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.25" thickBot="1">
+    <row r="12" spans="1:19" ht="17.25" thickBot="1">
       <c r="B12" s="78">
         <v>46161</v>
       </c>
@@ -4160,13 +4168,13 @@
         <v>1</v>
       </c>
       <c r="O12" s="102">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P12" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" thickBot="1">
+    <row r="13" spans="1:19" ht="17.25" thickBot="1">
       <c r="B13" s="78">
         <v>46162</v>
       </c>
@@ -4192,7 +4200,7 @@
         <v>15</v>
       </c>
       <c r="L13" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M13" s="35">
         <v>1</v>
@@ -4200,14 +4208,14 @@
       <c r="N13" s="35">
         <v>1</v>
       </c>
-      <c r="O13" s="102">
-        <v>39</v>
+      <c r="O13" s="95">
+        <v>45</v>
       </c>
       <c r="P13" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" thickBot="1">
+    <row r="14" spans="1:19" ht="17.25" thickBot="1">
       <c r="B14" s="78">
         <v>46163</v>
       </c>
@@ -4233,7 +4241,7 @@
         <v>16</v>
       </c>
       <c r="L14" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M14" s="35">
         <v>1</v>
@@ -4241,14 +4249,14 @@
       <c r="N14" s="35">
         <v>1</v>
       </c>
-      <c r="O14" s="102">
-        <v>36</v>
+      <c r="O14" s="95">
+        <v>42</v>
       </c>
       <c r="P14" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" thickBot="1">
+    <row r="15" spans="1:19" ht="17.25" thickBot="1">
       <c r="B15" s="78">
         <v>46164</v>
       </c>
@@ -4274,7 +4282,7 @@
         <v>17</v>
       </c>
       <c r="L15" s="35">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M15" s="35">
         <v>1</v>
@@ -4282,14 +4290,14 @@
       <c r="N15" s="35">
         <v>1</v>
       </c>
-      <c r="O15" s="102">
-        <v>46</v>
+      <c r="O15" s="95">
+        <v>52</v>
       </c>
       <c r="P15" s="36">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.25" thickBot="1">
+    <row r="16" spans="1:19" ht="17.25" thickBot="1">
       <c r="B16" s="81">
         <v>46167</v>
       </c>
@@ -4315,7 +4323,7 @@
         <v>77</v>
       </c>
       <c r="L16" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M16" s="39">
         <v>1</v>
@@ -4323,8 +4331,8 @@
       <c r="N16" s="39">
         <v>1</v>
       </c>
-      <c r="O16" s="103">
-        <v>33</v>
+      <c r="O16" s="95">
+        <v>39</v>
       </c>
       <c r="P16" s="40">
         <v>0</v>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C4A75D-26BF-40EC-9566-38D56BB7905A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C2A76E-5F88-4311-9D63-7719635A88AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29010" yWindow="255" windowWidth="11160" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="full stack" sheetId="8" r:id="rId1"/>

--- a/daily.xml.xlsx
+++ b/daily.xml.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyojung2\2026-AI-FULLSTACK-LevelUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C2A76E-5F88-4311-9D63-7719635A88AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9676A949-0AE8-4687-B4D0-1367B503DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29010" yWindow="255" windowWidth="11160" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="full stack" sheetId="8" r:id="rId1"/>
@@ -1951,7 +1951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2256,9 +2256,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3767,8 +3764,8 @@
       <c r="K3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="35">
-        <v>35</v>
+      <c r="L3" s="95">
+        <v>36</v>
       </c>
       <c r="M3" s="35">
         <v>1</v>
@@ -3777,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="95">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="36">
         <v>0</v>
@@ -3815,8 +3812,8 @@
       <c r="K4" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="35">
-        <v>35</v>
+      <c r="L4" s="95">
+        <v>36</v>
       </c>
       <c r="M4" s="35">
         <v>1</v>
@@ -3825,7 +3822,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="95">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="36">
         <v>0</v>
@@ -3859,8 +3856,8 @@
       <c r="K5" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="35">
-        <v>35</v>
+      <c r="L5" s="95">
+        <v>36</v>
       </c>
       <c r="M5" s="35">
         <v>1</v>
@@ -3869,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="95">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P5" s="36">
         <v>0</v>
@@ -3903,8 +3900,8 @@
       <c r="K6" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="35">
-        <v>35</v>
+      <c r="L6" s="95">
+        <v>36</v>
       </c>
       <c r="M6" s="35">
         <v>1</v>
@@ -3913,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="95">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P6" s="36">
         <v>0</v>
@@ -3950,8 +3947,8 @@
       <c r="K7" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="35">
-        <v>35</v>
+      <c r="L7" s="95">
+        <v>36</v>
       </c>
       <c r="M7" s="35">
         <v>1</v>
@@ -3960,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="95">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P7" s="36">
         <v>0</v>
@@ -3991,8 +3988,8 @@
       <c r="K8" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="35">
-        <v>34</v>
+      <c r="L8" s="95">
+        <v>35</v>
       </c>
       <c r="M8" s="35">
         <v>1</v>
@@ -4001,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="95">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P8" s="36">
         <v>0</v>
@@ -4032,8 +4029,8 @@
       <c r="K9" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="35">
-        <v>34</v>
+      <c r="L9" s="95">
+        <v>35</v>
       </c>
       <c r="M9" s="35">
         <v>1</v>
@@ -4042,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="95">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P9" s="36">
         <v>0</v>
@@ -4073,8 +4070,8 @@
       <c r="K10" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="35">
-        <v>35</v>
+      <c r="L10" s="95">
+        <v>36</v>
       </c>
       <c r="M10" s="35">
         <v>1</v>
@@ -4083,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="95">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P10" s="36">
         <v>0</v>
@@ -4117,8 +4114,8 @@
       <c r="K11" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="35">
-        <v>35</v>
+      <c r="L11" s="95">
+        <v>36</v>
       </c>
       <c r="M11" s="35">
         <v>1</v>
@@ -4127,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="95">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P11" s="36">
         <v>0</v>
@@ -4158,8 +4155,8 @@
       <c r="K12" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="35">
-        <v>26</v>
+      <c r="L12" s="95">
+        <v>27</v>
       </c>
       <c r="M12" s="35">
         <v>1</v>
@@ -4167,8 +4164,8 @@
       <c r="N12" s="35">
         <v>1</v>
       </c>
-      <c r="O12" s="102">
-        <v>34</v>
+      <c r="O12" s="95">
+        <v>35</v>
       </c>
       <c r="P12" s="36">
         <v>0</v>
@@ -4199,8 +4196,8 @@
       <c r="K13" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="35">
-        <v>35</v>
+      <c r="L13" s="95">
+        <v>36</v>
       </c>
       <c r="M13" s="35">
         <v>1</v>
@@ -4209,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="95">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P13" s="36">
         <v>0</v>
@@ -4240,8 +4237,8 @@
       <c r="K14" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="35">
-        <v>35</v>
+      <c r="L14" s="95">
+        <v>36</v>
       </c>
       <c r="M14" s="35">
         <v>1</v>
@@ -4250,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="95">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P14" s="36">
         <v>0</v>
@@ -4281,8 +4278,8 @@
       <c r="K15" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="L15" s="35">
-        <v>35</v>
+      <c r="L15" s="95">
+        <v>36</v>
       </c>
       <c r="M15" s="35">
         <v>1</v>
@@ -4291,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="95">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P15" s="36">
         <v>0</v>
@@ -4322,8 +4319,8 @@
       <c r="K16" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="39">
-        <v>33</v>
+      <c r="L16" s="95">
+        <v>34</v>
       </c>
       <c r="M16" s="39">
         <v>1</v>
@@ -4332,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="95">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P16" s="40">
         <v>0</v>
